--- a/output/Data and Chart Outputs/china_nbs_market_prices_10day.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_market_prices_10day.xlsx
@@ -13,15 +13,16 @@
     <sheet name="Chart - steel prices" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Chart - non-ferrous metal price" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Chart - basic chemical prices" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Chart - solar and battery mater" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Chart - polymer and fibre price" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Chart - building material price" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Chart - fertiliser and agrochem" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Chart - farm product prices" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Chart - live hog prices" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Chart - forest product prices" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Data" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Series" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Chart - polysilicon prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Chart - lithium iron phosphate " sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Chart - polymer and fibre price" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Chart - building material price" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Chart - fertiliser and agrochem" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Chart - farm product prices" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Chart - live hog prices" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Chart - forest product prices" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Data" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Series" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,6 +503,269 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>China fertiliser and agrochemical prices (NBS) (to Sep/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - fertiliser and agrochem'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$B$2:$B$200</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart - fertiliser and agrochem'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$C$2:$C$200</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart - fertiliser and agrochem'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$D$2:$D$200</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart - fertiliser and agrochem'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$E$2:$E$200</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart - fertiliser and agrochem'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E87BA4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - fertiliser and agrochem'!$F$2:$F$200</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="16"/>
+        <tickMarkSkip val="16"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>yuan/tonne</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>China farm product prices (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -861,7 +1125,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -980,7 +1244,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2379,7 +2643,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China solar and battery material prices (NBS) (to Sep/26)</a:t>
+              <a:t>China polysilicon prices (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2393,7 +2657,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Chart - solar and battery mater'!B1</f>
+              <f>'Chart - polysilicon prices'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -2414,48 +2678,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - solar and battery mater'!$A$2:$A$26</f>
+              <f>'Chart - polysilicon prices'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - solar and battery mater'!$B$2:$B$26</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Chart - solar and battery mater'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - solar and battery mater'!$A$2:$A$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - solar and battery mater'!$C$2:$C$26</f>
+              <f>'Chart - polysilicon prices'!$B$2:$B$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2523,6 +2751,125 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>China lithium iron phosphate prices (NBS) (to Sep/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - lithium iron phosphate '!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart - lithium iron phosphate '!$A$2:$A$26</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - lithium iron phosphate '!$B$2:$B$26</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>yuan/tonne</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2785,7 +3132,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2976,269 +3323,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>China fertiliser and agrochemical prices (NBS) (to Sep/26)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Chart - fertiliser and agrochem'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$B$2:$B$200</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Chart - fertiliser and agrochem'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$C$2:$C$200</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Chart - fertiliser and agrochem'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$D$2:$D$200</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Chart - fertiliser and agrochem'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EDA100"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$E$2:$E$200</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Chart - fertiliser and agrochem'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$A$2:$A$200</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - fertiliser and agrochem'!$F$2:$F$200</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="low"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="16"/>
-        <tickMarkSkip val="16"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>yuan/tonne</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln>
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -3270,7 +3354,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -3297,6 +3381,33 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
@@ -3320,7 +3431,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -3459,7 +3570,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -3486,7 +3597,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -3513,7 +3624,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -3540,7 +3651,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -3875,7 +3986,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prices in yuan per tonne (live hogs: yuan per kg), average market transaction price in circulation for that 10-day period, nationwide (NBS's monitoring survey of the circulation sector). Column names are on the 'Series' sheet with the full product description and unit.</t>
+          <t>Prices in yuan per tonne (live hogs and polysilicon: yuan per kg; see the 'Series' sheet), average market transaction price in circulation for that 10-day period, nationwide (NBS's monitoring survey of the circulation sector). Column names are on the 'Series' sheet with the full product description and unit.</t>
         </is>
       </c>
     </row>
@@ -3927,6 +4038,2757 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D200"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cement P.O 42.5, bagged</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cement P.O 42.5, bulk</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Float glass (4.8/5mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>480.1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>437.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2340.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>44207</v>
+      </c>
+      <c r="B3" t="n">
+        <v>480.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>434.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2273.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>44217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>478.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>429.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2159.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B5" t="n">
+        <v>475.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>424</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2143.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>44248</v>
+      </c>
+      <c r="B6" t="n">
+        <v>469.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2115.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B7" t="n">
+        <v>465.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>416.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2211.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>44266</v>
+      </c>
+      <c r="B8" t="n">
+        <v>460</v>
+      </c>
+      <c r="C8" t="n">
+        <v>413.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2270.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>44276</v>
+      </c>
+      <c r="B9" t="n">
+        <v>465.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>417.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2279.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B10" t="n">
+        <v>468.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>428.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2292.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>44297</v>
+      </c>
+      <c r="B11" t="n">
+        <v>474.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>436</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>44307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>443.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B13" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>448.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>44327</v>
+      </c>
+      <c r="B14" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>44337</v>
+      </c>
+      <c r="B15" t="n">
+        <v>482.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>446.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2782.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B16" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>437</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2847.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>44358</v>
+      </c>
+      <c r="B17" t="n">
+        <v>459.3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2856.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>44368</v>
+      </c>
+      <c r="B18" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>413.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2867.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B19" t="n">
+        <v>450.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2889.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>44388</v>
+      </c>
+      <c r="B20" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2955.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>44398</v>
+      </c>
+      <c r="B21" t="n">
+        <v>430.7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3064.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B22" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3137.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>44419</v>
+      </c>
+      <c r="B23" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3140.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>44429</v>
+      </c>
+      <c r="B24" t="n">
+        <v>445.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3142.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B25" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>423.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3151.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>44450</v>
+      </c>
+      <c r="B26" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>460.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3137.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>44460</v>
+      </c>
+      <c r="B27" t="n">
+        <v>562.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>547.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3074.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B28" t="n">
+        <v>602.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>588.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2850.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>44480</v>
+      </c>
+      <c r="B29" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>616.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2808.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>44490</v>
+      </c>
+      <c r="B30" t="n">
+        <v>698.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>618.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2662.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B31" t="n">
+        <v>676.6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>598.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2441.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>44511</v>
+      </c>
+      <c r="B32" t="n">
+        <v>657.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>585.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2168.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>44521</v>
+      </c>
+      <c r="B33" t="n">
+        <v>638.6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>565.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2102.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B34" t="n">
+        <v>595.3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>539.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2180.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>44541</v>
+      </c>
+      <c r="B35" t="n">
+        <v>577.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>520.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2226.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>44551</v>
+      </c>
+      <c r="B36" t="n">
+        <v>551.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2177.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B37" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>487.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2085.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>44572</v>
+      </c>
+      <c r="B38" t="n">
+        <v>522.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>474.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2062.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>44582</v>
+      </c>
+      <c r="B39" t="n">
+        <v>522.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>470.7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2100.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>44603</v>
+      </c>
+      <c r="B40" t="n">
+        <v>517.6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>470.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2403.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>44613</v>
+      </c>
+      <c r="B41" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="C41" t="n">
+        <v>472.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2450.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B42" t="n">
+        <v>511.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>474.3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2396.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>44631</v>
+      </c>
+      <c r="B43" t="n">
+        <v>514.3</v>
+      </c>
+      <c r="C43" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2249.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>44641</v>
+      </c>
+      <c r="B44" t="n">
+        <v>519.5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>479</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2076.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B45" t="n">
+        <v>523.2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>474.1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>44662</v>
+      </c>
+      <c r="B46" t="n">
+        <v>516.9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>475.3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2050.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>44672</v>
+      </c>
+      <c r="B47" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>470.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2048.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B48" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2042.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44692</v>
+      </c>
+      <c r="B49" t="n">
+        <v>509.4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>454.4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1999.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>44702</v>
+      </c>
+      <c r="B50" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1923.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B51" t="n">
+        <v>454.1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1859.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>44723</v>
+      </c>
+      <c r="B52" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="C52" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1809.8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>44733</v>
+      </c>
+      <c r="B53" t="n">
+        <v>428.8</v>
+      </c>
+      <c r="C53" t="n">
+        <v>390.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1782.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B54" t="n">
+        <v>416.9</v>
+      </c>
+      <c r="C54" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1762.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>44753</v>
+      </c>
+      <c r="B55" t="n">
+        <v>408.6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1732.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>44763</v>
+      </c>
+      <c r="B56" t="n">
+        <v>403.1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1673.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B57" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1677.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>44784</v>
+      </c>
+      <c r="B58" t="n">
+        <v>423</v>
+      </c>
+      <c r="C58" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1750.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>44794</v>
+      </c>
+      <c r="B59" t="n">
+        <v>436.3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1747.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B60" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="C60" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>44815</v>
+      </c>
+      <c r="B61" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1695.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>44825</v>
+      </c>
+      <c r="B62" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>389.8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1700.9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B63" t="n">
+        <v>425.7</v>
+      </c>
+      <c r="C63" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1717.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>44845</v>
+      </c>
+      <c r="B64" t="n">
+        <v>429.2</v>
+      </c>
+      <c r="C64" t="n">
+        <v>401.9</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1734.3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>44855</v>
+      </c>
+      <c r="B65" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>407.3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1733.6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B66" t="n">
+        <v>440</v>
+      </c>
+      <c r="C66" t="n">
+        <v>410</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1699.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>44876</v>
+      </c>
+      <c r="B67" t="n">
+        <v>441</v>
+      </c>
+      <c r="C67" t="n">
+        <v>414.4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1653.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>44886</v>
+      </c>
+      <c r="B68" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="C68" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1641.4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B69" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="C69" t="n">
+        <v>411.7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1615.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>44906</v>
+      </c>
+      <c r="B70" t="n">
+        <v>448.7</v>
+      </c>
+      <c r="C70" t="n">
+        <v>406.8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1620.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>44916</v>
+      </c>
+      <c r="B71" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="C71" t="n">
+        <v>399.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1626.6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B72" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1671.9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>44937</v>
+      </c>
+      <c r="B73" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="C73" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1700.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B74" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="C74" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1761.4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>44968</v>
+      </c>
+      <c r="B75" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="C75" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1756.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>44978</v>
+      </c>
+      <c r="B76" t="n">
+        <v>414.3</v>
+      </c>
+      <c r="C76" t="n">
+        <v>394</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1745.6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B77" t="n">
+        <v>417.1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1738.4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>44996</v>
+      </c>
+      <c r="B78" t="n">
+        <v>411.4</v>
+      </c>
+      <c r="C78" t="n">
+        <v>404.2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1765.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>45006</v>
+      </c>
+      <c r="B79" t="n">
+        <v>421.4</v>
+      </c>
+      <c r="C79" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1798.3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>429.4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>401.2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1829.6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>45027</v>
+      </c>
+      <c r="B81" t="n">
+        <v>428.8</v>
+      </c>
+      <c r="C81" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1904.2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>45037</v>
+      </c>
+      <c r="B82" t="n">
+        <v>422.9</v>
+      </c>
+      <c r="C82" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2121.3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B83" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="C83" t="n">
+        <v>381.9</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2256.6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>45057</v>
+      </c>
+      <c r="B84" t="n">
+        <v>419.4</v>
+      </c>
+      <c r="C84" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2276.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>45067</v>
+      </c>
+      <c r="B85" t="n">
+        <v>415.5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2174.4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B86" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="C86" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2061.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>45088</v>
+      </c>
+      <c r="B87" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2025.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>45098</v>
+      </c>
+      <c r="B88" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="C88" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1966.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B89" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="C89" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1913.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>45118</v>
+      </c>
+      <c r="B90" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="C90" t="n">
+        <v>318</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1915.6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>45128</v>
+      </c>
+      <c r="B91" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>315</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1960.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B92" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>311.7</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2007.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>45149</v>
+      </c>
+      <c r="B93" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>306.5</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2086.9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>45159</v>
+      </c>
+      <c r="B94" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>305</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2086.4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B95" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2107.6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>45180</v>
+      </c>
+      <c r="B96" t="n">
+        <v>360.9</v>
+      </c>
+      <c r="C96" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2118.3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>45190</v>
+      </c>
+      <c r="B97" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="C97" t="n">
+        <v>303.7</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2115.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B98" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2129.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>45210</v>
+      </c>
+      <c r="B99" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="C99" t="n">
+        <v>312.9</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2150.6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>45220</v>
+      </c>
+      <c r="B100" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2123.9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B101" t="n">
+        <v>368</v>
+      </c>
+      <c r="C101" t="n">
+        <v>326.3</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2072.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>45241</v>
+      </c>
+      <c r="B102" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2011.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>45251</v>
+      </c>
+      <c r="B103" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>329.6</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1967.9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B104" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="C104" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1986.6</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>45271</v>
+      </c>
+      <c r="B105" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="C105" t="n">
+        <v>334</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>45281</v>
+      </c>
+      <c r="B106" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="C106" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2016.6</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B107" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="C107" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>45302</v>
+      </c>
+      <c r="B108" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="C108" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2040.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>45312</v>
+      </c>
+      <c r="B109" t="n">
+        <v>370.6</v>
+      </c>
+      <c r="C109" t="n">
+        <v>321</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2045.1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B110" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="C110" t="n">
+        <v>320.6</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2051.1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>45343</v>
+      </c>
+      <c r="B111" t="n">
+        <v>369.7</v>
+      </c>
+      <c r="C111" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2068.8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B112" t="n">
+        <v>370</v>
+      </c>
+      <c r="C112" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>45362</v>
+      </c>
+      <c r="B113" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="C113" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1916.1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>45372</v>
+      </c>
+      <c r="B114" t="n">
+        <v>360.9</v>
+      </c>
+      <c r="C114" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1808.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B115" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="C115" t="n">
+        <v>307.6</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>45393</v>
+      </c>
+      <c r="B116" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="C116" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1729.7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>45403</v>
+      </c>
+      <c r="B117" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="C117" t="n">
+        <v>306.6</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1708.2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B118" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="C118" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1701.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>45423</v>
+      </c>
+      <c r="B119" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="C119" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1704.8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>45433</v>
+      </c>
+      <c r="B120" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="C120" t="n">
+        <v>309.9</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1680.4</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B121" t="n">
+        <v>387.6</v>
+      </c>
+      <c r="C121" t="n">
+        <v>334.6</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1682.9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>45454</v>
+      </c>
+      <c r="B122" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="C122" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>45464</v>
+      </c>
+      <c r="B123" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="C123" t="n">
+        <v>338</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1650.2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B124" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="C124" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1596.2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>45484</v>
+      </c>
+      <c r="B125" t="n">
+        <v>379.2</v>
+      </c>
+      <c r="C125" t="n">
+        <v>338</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1538.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>45494</v>
+      </c>
+      <c r="B126" t="n">
+        <v>370</v>
+      </c>
+      <c r="C126" t="n">
+        <v>334.1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1479.7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B127" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="C127" t="n">
+        <v>326.9</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1458.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>45515</v>
+      </c>
+      <c r="B128" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="C128" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1443.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>45525</v>
+      </c>
+      <c r="B129" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="C129" t="n">
+        <v>322.3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1373.6</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B130" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="C130" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1318.8</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>45546</v>
+      </c>
+      <c r="B131" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="C131" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>45556</v>
+      </c>
+      <c r="B132" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="C132" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1168.3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B133" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B134" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="C134" t="n">
+        <v>343.4</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1255.7</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>45586</v>
+      </c>
+      <c r="B135" t="n">
+        <v>406.6</v>
+      </c>
+      <c r="C135" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1287.4</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B136" t="n">
+        <v>401</v>
+      </c>
+      <c r="C136" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1400.2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>45607</v>
+      </c>
+      <c r="B137" t="n">
+        <v>402.8</v>
+      </c>
+      <c r="C137" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1459.2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>45617</v>
+      </c>
+      <c r="B138" t="n">
+        <v>403.8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1432.7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B139" t="n">
+        <v>403.4</v>
+      </c>
+      <c r="C139" t="n">
+        <v>361</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1416.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>45637</v>
+      </c>
+      <c r="B140" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="C140" t="n">
+        <v>358</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1406.2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>45647</v>
+      </c>
+      <c r="B141" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="C141" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1396.8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B142" t="n">
+        <v>398.1</v>
+      </c>
+      <c r="C142" t="n">
+        <v>348.2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1377.1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B143" t="n">
+        <v>397.1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>345.1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1388.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B144" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="C144" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1403.8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B145" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="C145" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1405.1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B146" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="C146" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1383.4</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B147" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1349.6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B148" t="n">
+        <v>388.9</v>
+      </c>
+      <c r="C148" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1310.8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>45737</v>
+      </c>
+      <c r="B149" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="C149" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1308.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B150" t="n">
+        <v>376.1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>45758</v>
+      </c>
+      <c r="B151" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="C151" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1328.9</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n">
+        <v>45768</v>
+      </c>
+      <c r="B152" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="C152" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1331.9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B153" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="C153" t="n">
+        <v>323</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1318.3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n">
+        <v>45788</v>
+      </c>
+      <c r="B154" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="C154" t="n">
+        <v>316</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>45798</v>
+      </c>
+      <c r="B155" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="C155" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1271.4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B156" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="C156" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1238.9</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>45819</v>
+      </c>
+      <c r="B157" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="C157" t="n">
+        <v>297.7</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1213.4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>45829</v>
+      </c>
+      <c r="B158" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="C158" t="n">
+        <v>292.1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B159" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="C159" t="n">
+        <v>287.1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1203.3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>45849</v>
+      </c>
+      <c r="B160" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="C160" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1212.4</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B161" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="C161" t="n">
+        <v>271.3</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1268.9</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B162" t="n">
+        <v>354</v>
+      </c>
+      <c r="C162" t="n">
+        <v>269.8</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1271.5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B163" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1216.2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B164" t="n">
+        <v>346</v>
+      </c>
+      <c r="C164" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1190.8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B165" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="C165" t="n">
+        <v>271.7</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1194.7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B166" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>275.9</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1206.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B167" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="C167" t="n">
+        <v>282.1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1254.6</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B168" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="C168" t="n">
+        <v>282.1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B169" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="C169" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1212.3</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B170" t="n">
+        <v>355</v>
+      </c>
+      <c r="C170" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1200.6</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B171" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="C171" t="n">
+        <v>281</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1175.9</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B172" t="n">
+        <v>336</v>
+      </c>
+      <c r="C172" t="n">
+        <v>278.6</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1148.9</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B173" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="C173" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1165.8</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B174" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="C174" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1153.1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B175" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="C175" t="n">
+        <v>281.3</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1132.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C176" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1124.2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n">
+        <v>46033</v>
+      </c>
+      <c r="C177" t="n">
+        <v>278.9</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1139.7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n">
+        <v>46043</v>
+      </c>
+      <c r="C178" t="n">
+        <v>277.3</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1142.9</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C179" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1155.9</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C180" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1171.1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C181" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1175.4</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C182" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n">
+        <v>46102</v>
+      </c>
+      <c r="C183" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1197.1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C184" t="n">
+        <v>269.3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1191.4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n">
+        <v>46123</v>
+      </c>
+      <c r="C185" t="n">
+        <v>267</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1176.1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C186" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1154.5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C187" t="n">
+        <v>259.6</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1149.4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C188" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1150.3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C189" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1140.1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C190" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1125.3</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C191" t="n">
+        <v>260.2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1115.2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C192" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1113.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C193" t="n">
+        <v>256</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1108.2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C194" t="n">
+        <v>250</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1100.4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C195" t="n">
+        <v>246.4</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1098.9</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C196" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1095.6</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C197" t="n">
+        <v>249.1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1084.6</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C198" t="n">
+        <v>248.7</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1074.1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C199" t="n">
+        <v>250.7</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1074.9</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C200" t="n">
+        <v>258.8</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1101.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6912,7 +9774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12226,7 +15088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13848,7 +16710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16674,7 +19536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47830,7 +50692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48721,7 +51583,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>solar and battery material prices</t>
+          <t>polysilicon prices</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -48748,7 +51610,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>solar and battery material prices</t>
+          <t>lithium iron phosphate prices</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -71189,7 +74051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -71206,11 +74068,6 @@
           <t>Polysilicon (dense material)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Lithium iron phosphate (power type)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
@@ -71219,9 +74076,6 @@
       <c r="B2" t="n">
         <v>52.7</v>
       </c>
-      <c r="C2" t="n">
-        <v>49980</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -71230,9 +74084,6 @@
       <c r="B3" t="n">
         <v>55</v>
       </c>
-      <c r="C3" t="n">
-        <v>54157.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -71241,9 +74092,6 @@
       <c r="B4" t="n">
         <v>55</v>
       </c>
-      <c r="C4" t="n">
-        <v>57337</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -71252,9 +74100,6 @@
       <c r="B5" t="n">
         <v>50.9</v>
       </c>
-      <c r="C5" t="n">
-        <v>50505.9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -71263,9 +74108,6 @@
       <c r="B6" t="n">
         <v>50.4</v>
       </c>
-      <c r="C6" t="n">
-        <v>57131.3</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -71274,9 +74116,6 @@
       <c r="B7" t="n">
         <v>49.1</v>
       </c>
-      <c r="C7" t="n">
-        <v>54754.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -71285,9 +74124,6 @@
       <c r="B8" t="n">
         <v>46.8</v>
       </c>
-      <c r="C8" t="n">
-        <v>54135.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -71296,9 +74132,6 @@
       <c r="B9" t="n">
         <v>43.1</v>
       </c>
-      <c r="C9" t="n">
-        <v>54373</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -71307,9 +74140,6 @@
       <c r="B10" t="n">
         <v>36.4</v>
       </c>
-      <c r="C10" t="n">
-        <v>54753.5</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -71318,9 +74148,6 @@
       <c r="B11" t="n">
         <v>35.5</v>
       </c>
-      <c r="C11" t="n">
-        <v>56998.7</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -71329,9 +74156,6 @@
       <c r="B12" t="n">
         <v>35.4</v>
       </c>
-      <c r="C12" t="n">
-        <v>58603</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -71340,9 +74164,6 @@
       <c r="B13" t="n">
         <v>35</v>
       </c>
-      <c r="C13" t="n">
-        <v>62867.4</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -71351,9 +74172,6 @@
       <c r="B14" t="n">
         <v>35</v>
       </c>
-      <c r="C14" t="n">
-        <v>62386.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -71362,9 +74180,6 @@
       <c r="B15" t="n">
         <v>34.6</v>
       </c>
-      <c r="C15" t="n">
-        <v>59411.1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -71373,9 +74188,6 @@
       <c r="B16" t="n">
         <v>34.5</v>
       </c>
-      <c r="C16" t="n">
-        <v>57634.3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -71384,9 +74196,6 @@
       <c r="B17" t="n">
         <v>33.8</v>
       </c>
-      <c r="C17" t="n">
-        <v>58434.2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -71395,9 +74204,6 @@
       <c r="B18" t="n">
         <v>33</v>
       </c>
-      <c r="C18" t="n">
-        <v>54350.4</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -71406,9 +74212,6 @@
       <c r="B19" t="n">
         <v>33</v>
       </c>
-      <c r="C19" t="n">
-        <v>58666</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -71417,9 +74220,6 @@
       <c r="B20" t="n">
         <v>32.2</v>
       </c>
-      <c r="C20" t="n">
-        <v>55966.4</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -71428,9 +74228,6 @@
       <c r="B21" t="n">
         <v>31.5</v>
       </c>
-      <c r="C21" t="n">
-        <v>54368.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -71439,9 +74236,6 @@
       <c r="B22" t="n">
         <v>31.5</v>
       </c>
-      <c r="C22" t="n">
-        <v>53732.5</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -71450,9 +74244,6 @@
       <c r="B23" t="n">
         <v>35.4</v>
       </c>
-      <c r="C23" t="n">
-        <v>56114.5</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -71461,9 +74252,6 @@
       <c r="B24" t="n">
         <v>40.5</v>
       </c>
-      <c r="C24" t="n">
-        <v>56905.4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -71472,9 +74260,6 @@
       <c r="B25" t="n">
         <v>40.9</v>
       </c>
-      <c r="C25" t="n">
-        <v>55800.8</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -71482,9 +74267,6 @@
       </c>
       <c r="B26" t="n">
         <v>41</v>
-      </c>
-      <c r="C26" t="n">
-        <v>51881.1</v>
       </c>
     </row>
   </sheetData>
@@ -71494,6 +74276,236 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Lithium iron phosphate (power type)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B2" t="n">
+        <v>49980</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B3" t="n">
+        <v>54157.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57337</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B5" t="n">
+        <v>50505.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57131.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B7" t="n">
+        <v>54754.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B8" t="n">
+        <v>54135.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B9" t="n">
+        <v>54373</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B10" t="n">
+        <v>54753.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56998.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58603</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B13" t="n">
+        <v>62867.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B14" t="n">
+        <v>62386.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B15" t="n">
+        <v>59411.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57634.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58434.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B18" t="n">
+        <v>54350.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58666</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B20" t="n">
+        <v>55966.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B21" t="n">
+        <v>54368.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B22" t="n">
+        <v>53732.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56114.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56905.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B25" t="n">
+        <v>55800.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B26" t="n">
+        <v>51881.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -75446,2755 +78458,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D200"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Cement P.O 42.5, bagged</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Cement P.O 42.5, bulk</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Float glass (4.8/5mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B2" t="n">
-        <v>480.1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>437.7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2340.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>44207</v>
-      </c>
-      <c r="B3" t="n">
-        <v>480.4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>434.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2273.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>44217</v>
-      </c>
-      <c r="B4" t="n">
-        <v>478.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>429.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2159.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B5" t="n">
-        <v>475.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>424</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2143.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>44248</v>
-      </c>
-      <c r="B6" t="n">
-        <v>469.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>417.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2115.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B7" t="n">
-        <v>465.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>416.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2211.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>44266</v>
-      </c>
-      <c r="B8" t="n">
-        <v>460</v>
-      </c>
-      <c r="C8" t="n">
-        <v>413.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2270.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>44276</v>
-      </c>
-      <c r="B9" t="n">
-        <v>465.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>417.4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2279.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B10" t="n">
-        <v>468.6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>428.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2292.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>44297</v>
-      </c>
-      <c r="B11" t="n">
-        <v>474.9</v>
-      </c>
-      <c r="C11" t="n">
-        <v>436</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2342</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>44307</v>
-      </c>
-      <c r="B12" t="n">
-        <v>479.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>443.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2374</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B13" t="n">
-        <v>487.9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>448.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>44327</v>
-      </c>
-      <c r="B14" t="n">
-        <v>487.9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>450.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2619</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>44337</v>
-      </c>
-      <c r="B15" t="n">
-        <v>482.3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>446.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2782.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B16" t="n">
-        <v>469.9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>437</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2847.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>44358</v>
-      </c>
-      <c r="B17" t="n">
-        <v>459.3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>427.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2856.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>44368</v>
-      </c>
-      <c r="B18" t="n">
-        <v>454.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2867.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B19" t="n">
-        <v>450.3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>399.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2889.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>44388</v>
-      </c>
-      <c r="B20" t="n">
-        <v>437.6</v>
-      </c>
-      <c r="C20" t="n">
-        <v>386.4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2955.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>44398</v>
-      </c>
-      <c r="B21" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>379.3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3064.8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B22" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="C22" t="n">
-        <v>385.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3137.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>44419</v>
-      </c>
-      <c r="B23" t="n">
-        <v>438.2</v>
-      </c>
-      <c r="C23" t="n">
-        <v>397.8</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3140.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>44429</v>
-      </c>
-      <c r="B24" t="n">
-        <v>445.7</v>
-      </c>
-      <c r="C24" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3142.7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B25" t="n">
-        <v>466.4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>423.6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3151.7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>44450</v>
-      </c>
-      <c r="B26" t="n">
-        <v>481.4</v>
-      </c>
-      <c r="C26" t="n">
-        <v>460.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3137.1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>44460</v>
-      </c>
-      <c r="B27" t="n">
-        <v>562.2</v>
-      </c>
-      <c r="C27" t="n">
-        <v>547.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3074.3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B28" t="n">
-        <v>602.9</v>
-      </c>
-      <c r="C28" t="n">
-        <v>588.3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2850.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>44480</v>
-      </c>
-      <c r="B29" t="n">
-        <v>665.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>616.3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2808.6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>44490</v>
-      </c>
-      <c r="B30" t="n">
-        <v>698.6</v>
-      </c>
-      <c r="C30" t="n">
-        <v>618.9</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2662.9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B31" t="n">
-        <v>676.6</v>
-      </c>
-      <c r="C31" t="n">
-        <v>598.8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2441.2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>44511</v>
-      </c>
-      <c r="B32" t="n">
-        <v>657.4</v>
-      </c>
-      <c r="C32" t="n">
-        <v>585.7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2168.9</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>44521</v>
-      </c>
-      <c r="B33" t="n">
-        <v>638.6</v>
-      </c>
-      <c r="C33" t="n">
-        <v>565.1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2102.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B34" t="n">
-        <v>595.3</v>
-      </c>
-      <c r="C34" t="n">
-        <v>539.5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2180.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>44541</v>
-      </c>
-      <c r="B35" t="n">
-        <v>577.4</v>
-      </c>
-      <c r="C35" t="n">
-        <v>520.9</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2226.7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>44551</v>
-      </c>
-      <c r="B36" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="C36" t="n">
-        <v>509.1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2177.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B37" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>487.7</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2085.4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>44572</v>
-      </c>
-      <c r="B38" t="n">
-        <v>522.1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>474.9</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2062.9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>44582</v>
-      </c>
-      <c r="B39" t="n">
-        <v>522.1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>470.7</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2100.3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
-        <v>44603</v>
-      </c>
-      <c r="B40" t="n">
-        <v>517.6</v>
-      </c>
-      <c r="C40" t="n">
-        <v>470.1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2403.1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>44613</v>
-      </c>
-      <c r="B41" t="n">
-        <v>515.7</v>
-      </c>
-      <c r="C41" t="n">
-        <v>472.2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2450.5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B42" t="n">
-        <v>511.9</v>
-      </c>
-      <c r="C42" t="n">
-        <v>474.3</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2396.8</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>44631</v>
-      </c>
-      <c r="B43" t="n">
-        <v>514.3</v>
-      </c>
-      <c r="C43" t="n">
-        <v>480.9</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2249.6</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>44641</v>
-      </c>
-      <c r="B44" t="n">
-        <v>519.5</v>
-      </c>
-      <c r="C44" t="n">
-        <v>479</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2076.6</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B45" t="n">
-        <v>523.2</v>
-      </c>
-      <c r="C45" t="n">
-        <v>474.1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>44662</v>
-      </c>
-      <c r="B46" t="n">
-        <v>516.9</v>
-      </c>
-      <c r="C46" t="n">
-        <v>475.3</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2050.6</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>44672</v>
-      </c>
-      <c r="B47" t="n">
-        <v>516.1</v>
-      </c>
-      <c r="C47" t="n">
-        <v>470.4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2048.4</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B48" t="n">
-        <v>515.7</v>
-      </c>
-      <c r="C48" t="n">
-        <v>460.8</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2042.1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>44692</v>
-      </c>
-      <c r="B49" t="n">
-        <v>509.4</v>
-      </c>
-      <c r="C49" t="n">
-        <v>454.4</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1999.2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="n">
-        <v>44702</v>
-      </c>
-      <c r="B50" t="n">
-        <v>482.5</v>
-      </c>
-      <c r="C50" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1923.8</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B51" t="n">
-        <v>454.1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1859.1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>44723</v>
-      </c>
-      <c r="B52" t="n">
-        <v>444.9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>402.1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1809.8</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>44733</v>
-      </c>
-      <c r="B53" t="n">
-        <v>428.8</v>
-      </c>
-      <c r="C53" t="n">
-        <v>390.1</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1782.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B54" t="n">
-        <v>416.9</v>
-      </c>
-      <c r="C54" t="n">
-        <v>377.8</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1762.8</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>44753</v>
-      </c>
-      <c r="B55" t="n">
-        <v>408.6</v>
-      </c>
-      <c r="C55" t="n">
-        <v>369.1</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1732.6</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="n">
-        <v>44763</v>
-      </c>
-      <c r="B56" t="n">
-        <v>403.1</v>
-      </c>
-      <c r="C56" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1673.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B57" t="n">
-        <v>416.4</v>
-      </c>
-      <c r="C57" t="n">
-        <v>370.4</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1677.2</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>44784</v>
-      </c>
-      <c r="B58" t="n">
-        <v>423</v>
-      </c>
-      <c r="C58" t="n">
-        <v>372.9</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1750.9</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="n">
-        <v>44794</v>
-      </c>
-      <c r="B59" t="n">
-        <v>436.3</v>
-      </c>
-      <c r="C59" t="n">
-        <v>384.3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1747.9</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B60" t="n">
-        <v>429.8</v>
-      </c>
-      <c r="C60" t="n">
-        <v>385.6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="n">
-        <v>44815</v>
-      </c>
-      <c r="B61" t="n">
-        <v>429.8</v>
-      </c>
-      <c r="C61" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1695.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="n">
-        <v>44825</v>
-      </c>
-      <c r="B62" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="C62" t="n">
-        <v>389.8</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1700.9</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B63" t="n">
-        <v>425.7</v>
-      </c>
-      <c r="C63" t="n">
-        <v>397.7</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1717.7</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="n">
-        <v>44845</v>
-      </c>
-      <c r="B64" t="n">
-        <v>429.2</v>
-      </c>
-      <c r="C64" t="n">
-        <v>401.9</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1734.3</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="n">
-        <v>44855</v>
-      </c>
-      <c r="B65" t="n">
-        <v>434.5</v>
-      </c>
-      <c r="C65" t="n">
-        <v>407.3</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1733.6</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B66" t="n">
-        <v>440</v>
-      </c>
-      <c r="C66" t="n">
-        <v>410</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1699.8</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="n">
-        <v>44876</v>
-      </c>
-      <c r="B67" t="n">
-        <v>441</v>
-      </c>
-      <c r="C67" t="n">
-        <v>414.4</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1653.3</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="n">
-        <v>44886</v>
-      </c>
-      <c r="B68" t="n">
-        <v>453.6</v>
-      </c>
-      <c r="C68" t="n">
-        <v>416.4</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1641.4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B69" t="n">
-        <v>451.9</v>
-      </c>
-      <c r="C69" t="n">
-        <v>411.7</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1615.8</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="n">
-        <v>44906</v>
-      </c>
-      <c r="B70" t="n">
-        <v>448.7</v>
-      </c>
-      <c r="C70" t="n">
-        <v>406.8</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1620.6</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="n">
-        <v>44916</v>
-      </c>
-      <c r="B71" t="n">
-        <v>436.6</v>
-      </c>
-      <c r="C71" t="n">
-        <v>399.7</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1626.6</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B72" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="C72" t="n">
-        <v>390.3</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1671.9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n">
-        <v>44937</v>
-      </c>
-      <c r="B73" t="n">
-        <v>416.4</v>
-      </c>
-      <c r="C73" t="n">
-        <v>387.1</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1700.6</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B74" t="n">
-        <v>411.9</v>
-      </c>
-      <c r="C74" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1761.4</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="n">
-        <v>44968</v>
-      </c>
-      <c r="B75" t="n">
-        <v>416.4</v>
-      </c>
-      <c r="C75" t="n">
-        <v>389.9</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1756.6</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="n">
-        <v>44978</v>
-      </c>
-      <c r="B76" t="n">
-        <v>414.3</v>
-      </c>
-      <c r="C76" t="n">
-        <v>394</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1745.6</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B77" t="n">
-        <v>417.1</v>
-      </c>
-      <c r="C77" t="n">
-        <v>400.2</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1738.4</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="n">
-        <v>44996</v>
-      </c>
-      <c r="B78" t="n">
-        <v>411.4</v>
-      </c>
-      <c r="C78" t="n">
-        <v>404.2</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1765.7</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="n">
-        <v>45006</v>
-      </c>
-      <c r="B79" t="n">
-        <v>421.4</v>
-      </c>
-      <c r="C79" t="n">
-        <v>403.2</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1798.3</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B80" t="n">
-        <v>429.4</v>
-      </c>
-      <c r="C80" t="n">
-        <v>401.2</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1829.6</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="n">
-        <v>45027</v>
-      </c>
-      <c r="B81" t="n">
-        <v>428.8</v>
-      </c>
-      <c r="C81" t="n">
-        <v>395.5</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1904.2</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="n">
-        <v>45037</v>
-      </c>
-      <c r="B82" t="n">
-        <v>422.9</v>
-      </c>
-      <c r="C82" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="D82" t="n">
-        <v>2121.3</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B83" t="n">
-        <v>423.8</v>
-      </c>
-      <c r="C83" t="n">
-        <v>381.9</v>
-      </c>
-      <c r="D83" t="n">
-        <v>2256.6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="n">
-        <v>45057</v>
-      </c>
-      <c r="B84" t="n">
-        <v>419.4</v>
-      </c>
-      <c r="C84" t="n">
-        <v>373.8</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2276.3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="n">
-        <v>45067</v>
-      </c>
-      <c r="B85" t="n">
-        <v>415.5</v>
-      </c>
-      <c r="C85" t="n">
-        <v>360.3</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2174.4</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B86" t="n">
-        <v>399.6</v>
-      </c>
-      <c r="C86" t="n">
-        <v>351.1</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2061.3</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n">
-        <v>45088</v>
-      </c>
-      <c r="B87" t="n">
-        <v>391.1</v>
-      </c>
-      <c r="C87" t="n">
-        <v>342.2</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2025.7</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="n">
-        <v>45098</v>
-      </c>
-      <c r="B88" t="n">
-        <v>383.9</v>
-      </c>
-      <c r="C88" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1966.8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B89" t="n">
-        <v>377.7</v>
-      </c>
-      <c r="C89" t="n">
-        <v>323.6</v>
-      </c>
-      <c r="D89" t="n">
-        <v>1913.1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="n">
-        <v>45118</v>
-      </c>
-      <c r="B90" t="n">
-        <v>375.5</v>
-      </c>
-      <c r="C90" t="n">
-        <v>318</v>
-      </c>
-      <c r="D90" t="n">
-        <v>1915.6</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="n">
-        <v>45128</v>
-      </c>
-      <c r="B91" t="n">
-        <v>382.1</v>
-      </c>
-      <c r="C91" t="n">
-        <v>315</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1960.4</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B92" t="n">
-        <v>381.1</v>
-      </c>
-      <c r="C92" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2007.5</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n">
-        <v>45149</v>
-      </c>
-      <c r="B93" t="n">
-        <v>375.1</v>
-      </c>
-      <c r="C93" t="n">
-        <v>306.5</v>
-      </c>
-      <c r="D93" t="n">
-        <v>2086.9</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>45159</v>
-      </c>
-      <c r="B94" t="n">
-        <v>367.3</v>
-      </c>
-      <c r="C94" t="n">
-        <v>305</v>
-      </c>
-      <c r="D94" t="n">
-        <v>2086.4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B95" t="n">
-        <v>360.5</v>
-      </c>
-      <c r="C95" t="n">
-        <v>300.6</v>
-      </c>
-      <c r="D95" t="n">
-        <v>2107.6</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="n">
-        <v>45180</v>
-      </c>
-      <c r="B96" t="n">
-        <v>360.9</v>
-      </c>
-      <c r="C96" t="n">
-        <v>300.3</v>
-      </c>
-      <c r="D96" t="n">
-        <v>2118.3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="n">
-        <v>45190</v>
-      </c>
-      <c r="B97" t="n">
-        <v>358.8</v>
-      </c>
-      <c r="C97" t="n">
-        <v>303.7</v>
-      </c>
-      <c r="D97" t="n">
-        <v>2115.5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B98" t="n">
-        <v>356.8</v>
-      </c>
-      <c r="C98" t="n">
-        <v>306.3</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2129.5</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="n">
-        <v>45210</v>
-      </c>
-      <c r="B99" t="n">
-        <v>355.5</v>
-      </c>
-      <c r="C99" t="n">
-        <v>312.9</v>
-      </c>
-      <c r="D99" t="n">
-        <v>2150.6</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="n">
-        <v>45220</v>
-      </c>
-      <c r="B100" t="n">
-        <v>363.4</v>
-      </c>
-      <c r="C100" t="n">
-        <v>322.1</v>
-      </c>
-      <c r="D100" t="n">
-        <v>2123.9</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B101" t="n">
-        <v>368</v>
-      </c>
-      <c r="C101" t="n">
-        <v>326.3</v>
-      </c>
-      <c r="D101" t="n">
-        <v>2072.5</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="n">
-        <v>45241</v>
-      </c>
-      <c r="B102" t="n">
-        <v>371.2</v>
-      </c>
-      <c r="C102" t="n">
-        <v>328.3</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2011.5</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="n">
-        <v>45251</v>
-      </c>
-      <c r="B103" t="n">
-        <v>373.1</v>
-      </c>
-      <c r="C103" t="n">
-        <v>329.6</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1967.9</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B104" t="n">
-        <v>373.9</v>
-      </c>
-      <c r="C104" t="n">
-        <v>336.4</v>
-      </c>
-      <c r="D104" t="n">
-        <v>1986.6</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="n">
-        <v>45271</v>
-      </c>
-      <c r="B105" t="n">
-        <v>371.8</v>
-      </c>
-      <c r="C105" t="n">
-        <v>334</v>
-      </c>
-      <c r="D105" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="n">
-        <v>45281</v>
-      </c>
-      <c r="B106" t="n">
-        <v>371.4</v>
-      </c>
-      <c r="C106" t="n">
-        <v>334.2</v>
-      </c>
-      <c r="D106" t="n">
-        <v>2016.6</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B107" t="n">
-        <v>371.7</v>
-      </c>
-      <c r="C107" t="n">
-        <v>329.2</v>
-      </c>
-      <c r="D107" t="n">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="n">
-        <v>45302</v>
-      </c>
-      <c r="B108" t="n">
-        <v>367.4</v>
-      </c>
-      <c r="C108" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="D108" t="n">
-        <v>2040.4</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n">
-        <v>45312</v>
-      </c>
-      <c r="B109" t="n">
-        <v>370.6</v>
-      </c>
-      <c r="C109" t="n">
-        <v>321</v>
-      </c>
-      <c r="D109" t="n">
-        <v>2045.1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B110" t="n">
-        <v>371.4</v>
-      </c>
-      <c r="C110" t="n">
-        <v>320.6</v>
-      </c>
-      <c r="D110" t="n">
-        <v>2051.1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="n">
-        <v>45343</v>
-      </c>
-      <c r="B111" t="n">
-        <v>369.7</v>
-      </c>
-      <c r="C111" t="n">
-        <v>319.7</v>
-      </c>
-      <c r="D111" t="n">
-        <v>2068.8</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B112" t="n">
-        <v>370</v>
-      </c>
-      <c r="C112" t="n">
-        <v>319.7</v>
-      </c>
-      <c r="D112" t="n">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="n">
-        <v>45362</v>
-      </c>
-      <c r="B113" t="n">
-        <v>370.7</v>
-      </c>
-      <c r="C113" t="n">
-        <v>318.8</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1916.1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="n">
-        <v>45372</v>
-      </c>
-      <c r="B114" t="n">
-        <v>360.9</v>
-      </c>
-      <c r="C114" t="n">
-        <v>312.8</v>
-      </c>
-      <c r="D114" t="n">
-        <v>1808.9</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B115" t="n">
-        <v>352.9</v>
-      </c>
-      <c r="C115" t="n">
-        <v>307.6</v>
-      </c>
-      <c r="D115" t="n">
-        <v>1734</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="n">
-        <v>45393</v>
-      </c>
-      <c r="B116" t="n">
-        <v>357.4</v>
-      </c>
-      <c r="C116" t="n">
-        <v>309.6</v>
-      </c>
-      <c r="D116" t="n">
-        <v>1729.7</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="n">
-        <v>45403</v>
-      </c>
-      <c r="B117" t="n">
-        <v>351.9</v>
-      </c>
-      <c r="C117" t="n">
-        <v>306.6</v>
-      </c>
-      <c r="D117" t="n">
-        <v>1708.2</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B118" t="n">
-        <v>358.8</v>
-      </c>
-      <c r="C118" t="n">
-        <v>300.3</v>
-      </c>
-      <c r="D118" t="n">
-        <v>1701.1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="n">
-        <v>45423</v>
-      </c>
-      <c r="B119" t="n">
-        <v>359.2</v>
-      </c>
-      <c r="C119" t="n">
-        <v>301.1</v>
-      </c>
-      <c r="D119" t="n">
-        <v>1704.8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="n">
-        <v>45433</v>
-      </c>
-      <c r="B120" t="n">
-        <v>360.6</v>
-      </c>
-      <c r="C120" t="n">
-        <v>309.9</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1680.4</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B121" t="n">
-        <v>387.6</v>
-      </c>
-      <c r="C121" t="n">
-        <v>334.6</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1682.9</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="n">
-        <v>45454</v>
-      </c>
-      <c r="B122" t="n">
-        <v>384.3</v>
-      </c>
-      <c r="C122" t="n">
-        <v>338.7</v>
-      </c>
-      <c r="D122" t="n">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="n">
-        <v>45464</v>
-      </c>
-      <c r="B123" t="n">
-        <v>380.8</v>
-      </c>
-      <c r="C123" t="n">
-        <v>338</v>
-      </c>
-      <c r="D123" t="n">
-        <v>1650.2</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B124" t="n">
-        <v>380.5</v>
-      </c>
-      <c r="C124" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D124" t="n">
-        <v>1596.2</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="n">
-        <v>45484</v>
-      </c>
-      <c r="B125" t="n">
-        <v>379.2</v>
-      </c>
-      <c r="C125" t="n">
-        <v>338</v>
-      </c>
-      <c r="D125" t="n">
-        <v>1538.2</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="n">
-        <v>45494</v>
-      </c>
-      <c r="B126" t="n">
-        <v>370</v>
-      </c>
-      <c r="C126" t="n">
-        <v>334.1</v>
-      </c>
-      <c r="D126" t="n">
-        <v>1479.7</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="n">
-        <v>45505</v>
-      </c>
-      <c r="B127" t="n">
-        <v>366.9</v>
-      </c>
-      <c r="C127" t="n">
-        <v>326.9</v>
-      </c>
-      <c r="D127" t="n">
-        <v>1458.5</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="n">
-        <v>45515</v>
-      </c>
-      <c r="B128" t="n">
-        <v>363.3</v>
-      </c>
-      <c r="C128" t="n">
-        <v>324.2</v>
-      </c>
-      <c r="D128" t="n">
-        <v>1443.5</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="n">
-        <v>45525</v>
-      </c>
-      <c r="B129" t="n">
-        <v>360.4</v>
-      </c>
-      <c r="C129" t="n">
-        <v>322.3</v>
-      </c>
-      <c r="D129" t="n">
-        <v>1373.6</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="n">
-        <v>45536</v>
-      </c>
-      <c r="B130" t="n">
-        <v>363.7</v>
-      </c>
-      <c r="C130" t="n">
-        <v>322.9</v>
-      </c>
-      <c r="D130" t="n">
-        <v>1318.8</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="n">
-        <v>45546</v>
-      </c>
-      <c r="B131" t="n">
-        <v>369.5</v>
-      </c>
-      <c r="C131" t="n">
-        <v>322.5</v>
-      </c>
-      <c r="D131" t="n">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="n">
-        <v>45556</v>
-      </c>
-      <c r="B132" t="n">
-        <v>373.2</v>
-      </c>
-      <c r="C132" t="n">
-        <v>322.7</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1168.3</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B133" t="n">
-        <v>389.6</v>
-      </c>
-      <c r="C133" t="n">
-        <v>338.8</v>
-      </c>
-      <c r="D133" t="n">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="n">
-        <v>45576</v>
-      </c>
-      <c r="B134" t="n">
-        <v>399.6</v>
-      </c>
-      <c r="C134" t="n">
-        <v>343.4</v>
-      </c>
-      <c r="D134" t="n">
-        <v>1255.7</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="n">
-        <v>45586</v>
-      </c>
-      <c r="B135" t="n">
-        <v>406.6</v>
-      </c>
-      <c r="C135" t="n">
-        <v>351.5</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1287.4</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B136" t="n">
-        <v>401</v>
-      </c>
-      <c r="C136" t="n">
-        <v>359.2</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1400.2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="n">
-        <v>45607</v>
-      </c>
-      <c r="B137" t="n">
-        <v>402.8</v>
-      </c>
-      <c r="C137" t="n">
-        <v>362.3</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1459.2</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="n">
-        <v>45617</v>
-      </c>
-      <c r="B138" t="n">
-        <v>403.8</v>
-      </c>
-      <c r="C138" t="n">
-        <v>363.4</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1432.7</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B139" t="n">
-        <v>403.4</v>
-      </c>
-      <c r="C139" t="n">
-        <v>361</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1416.7</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="n">
-        <v>45637</v>
-      </c>
-      <c r="B140" t="n">
-        <v>403.2</v>
-      </c>
-      <c r="C140" t="n">
-        <v>358</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1406.2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="n">
-        <v>45647</v>
-      </c>
-      <c r="B141" t="n">
-        <v>403.2</v>
-      </c>
-      <c r="C141" t="n">
-        <v>353.9</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1396.8</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B142" t="n">
-        <v>398.1</v>
-      </c>
-      <c r="C142" t="n">
-        <v>348.2</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1377.1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="n">
-        <v>45668</v>
-      </c>
-      <c r="B143" t="n">
-        <v>397.1</v>
-      </c>
-      <c r="C143" t="n">
-        <v>345.1</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1388.6</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="n">
-        <v>45689</v>
-      </c>
-      <c r="B144" t="n">
-        <v>390.7</v>
-      </c>
-      <c r="C144" t="n">
-        <v>340.5</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1403.8</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B145" t="n">
-        <v>389.2</v>
-      </c>
-      <c r="C145" t="n">
-        <v>336.7</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1405.1</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B146" t="n">
-        <v>385.3</v>
-      </c>
-      <c r="C146" t="n">
-        <v>338.2</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1383.4</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="5" t="n">
-        <v>45717</v>
-      </c>
-      <c r="B147" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="C147" t="n">
-        <v>343.5</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1349.6</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B148" t="n">
-        <v>388.9</v>
-      </c>
-      <c r="C148" t="n">
-        <v>352.1</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1310.8</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="n">
-        <v>45737</v>
-      </c>
-      <c r="B149" t="n">
-        <v>385.8</v>
-      </c>
-      <c r="C149" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1308.3</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B150" t="n">
-        <v>376.1</v>
-      </c>
-      <c r="C150" t="n">
-        <v>343.5</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="n">
-        <v>45758</v>
-      </c>
-      <c r="B151" t="n">
-        <v>374.3</v>
-      </c>
-      <c r="C151" t="n">
-        <v>335.3</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1328.9</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="5" t="n">
-        <v>45768</v>
-      </c>
-      <c r="B152" t="n">
-        <v>377.3</v>
-      </c>
-      <c r="C152" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1331.9</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B153" t="n">
-        <v>374.8</v>
-      </c>
-      <c r="C153" t="n">
-        <v>323</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1318.3</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="5" t="n">
-        <v>45788</v>
-      </c>
-      <c r="B154" t="n">
-        <v>370.9</v>
-      </c>
-      <c r="C154" t="n">
-        <v>316</v>
-      </c>
-      <c r="D154" t="n">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="n">
-        <v>45798</v>
-      </c>
-      <c r="B155" t="n">
-        <v>370.1</v>
-      </c>
-      <c r="C155" t="n">
-        <v>308.1</v>
-      </c>
-      <c r="D155" t="n">
-        <v>1271.4</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="5" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B156" t="n">
-        <v>366.4</v>
-      </c>
-      <c r="C156" t="n">
-        <v>302.2</v>
-      </c>
-      <c r="D156" t="n">
-        <v>1238.9</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="5" t="n">
-        <v>45819</v>
-      </c>
-      <c r="B157" t="n">
-        <v>370.1</v>
-      </c>
-      <c r="C157" t="n">
-        <v>297.7</v>
-      </c>
-      <c r="D157" t="n">
-        <v>1213.4</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="5" t="n">
-        <v>45829</v>
-      </c>
-      <c r="B158" t="n">
-        <v>370.7</v>
-      </c>
-      <c r="C158" t="n">
-        <v>292.1</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="5" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B159" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="C159" t="n">
-        <v>287.1</v>
-      </c>
-      <c r="D159" t="n">
-        <v>1203.3</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="5" t="n">
-        <v>45849</v>
-      </c>
-      <c r="B160" t="n">
-        <v>362.4</v>
-      </c>
-      <c r="C160" t="n">
-        <v>277.2</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1212.4</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="n">
-        <v>45859</v>
-      </c>
-      <c r="B161" t="n">
-        <v>355.7</v>
-      </c>
-      <c r="C161" t="n">
-        <v>271.3</v>
-      </c>
-      <c r="D161" t="n">
-        <v>1268.9</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="5" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B162" t="n">
-        <v>354</v>
-      </c>
-      <c r="C162" t="n">
-        <v>269.8</v>
-      </c>
-      <c r="D162" t="n">
-        <v>1271.5</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="n">
-        <v>45880</v>
-      </c>
-      <c r="B163" t="n">
-        <v>348.6</v>
-      </c>
-      <c r="C163" t="n">
-        <v>272.4</v>
-      </c>
-      <c r="D163" t="n">
-        <v>1216.2</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="n">
-        <v>45890</v>
-      </c>
-      <c r="B164" t="n">
-        <v>346</v>
-      </c>
-      <c r="C164" t="n">
-        <v>272.8</v>
-      </c>
-      <c r="D164" t="n">
-        <v>1190.8</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B165" t="n">
-        <v>340.4</v>
-      </c>
-      <c r="C165" t="n">
-        <v>271.7</v>
-      </c>
-      <c r="D165" t="n">
-        <v>1194.7</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="5" t="n">
-        <v>45911</v>
-      </c>
-      <c r="B166" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="C166" t="n">
-        <v>275.9</v>
-      </c>
-      <c r="D166" t="n">
-        <v>1206.2</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="n">
-        <v>45921</v>
-      </c>
-      <c r="B167" t="n">
-        <v>348.5</v>
-      </c>
-      <c r="C167" t="n">
-        <v>282.1</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1254.6</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B168" t="n">
-        <v>352.1</v>
-      </c>
-      <c r="C168" t="n">
-        <v>282.1</v>
-      </c>
-      <c r="D168" t="n">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B169" t="n">
-        <v>350.9</v>
-      </c>
-      <c r="C169" t="n">
-        <v>283.3</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1212.3</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="5" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B170" t="n">
-        <v>355</v>
-      </c>
-      <c r="C170" t="n">
-        <v>284.6</v>
-      </c>
-      <c r="D170" t="n">
-        <v>1200.6</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="n">
-        <v>45972</v>
-      </c>
-      <c r="B171" t="n">
-        <v>345.2</v>
-      </c>
-      <c r="C171" t="n">
-        <v>281</v>
-      </c>
-      <c r="D171" t="n">
-        <v>1175.9</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="n">
-        <v>45982</v>
-      </c>
-      <c r="B172" t="n">
-        <v>336</v>
-      </c>
-      <c r="C172" t="n">
-        <v>278.6</v>
-      </c>
-      <c r="D172" t="n">
-        <v>1148.9</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B173" t="n">
-        <v>329.5</v>
-      </c>
-      <c r="C173" t="n">
-        <v>281.5</v>
-      </c>
-      <c r="D173" t="n">
-        <v>1165.8</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="n">
-        <v>46002</v>
-      </c>
-      <c r="B174" t="n">
-        <v>331.9</v>
-      </c>
-      <c r="C174" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="D174" t="n">
-        <v>1153.1</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="5" t="n">
-        <v>46012</v>
-      </c>
-      <c r="B175" t="n">
-        <v>328.2</v>
-      </c>
-      <c r="C175" t="n">
-        <v>281.3</v>
-      </c>
-      <c r="D175" t="n">
-        <v>1132.5</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="C176" t="n">
-        <v>279.5</v>
-      </c>
-      <c r="D176" t="n">
-        <v>1124.2</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="5" t="n">
-        <v>46033</v>
-      </c>
-      <c r="C177" t="n">
-        <v>278.9</v>
-      </c>
-      <c r="D177" t="n">
-        <v>1139.7</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="n">
-        <v>46043</v>
-      </c>
-      <c r="C178" t="n">
-        <v>277.3</v>
-      </c>
-      <c r="D178" t="n">
-        <v>1142.9</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="n">
-        <v>46054</v>
-      </c>
-      <c r="C179" t="n">
-        <v>275.5</v>
-      </c>
-      <c r="D179" t="n">
-        <v>1155.9</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="n">
-        <v>46074</v>
-      </c>
-      <c r="C180" t="n">
-        <v>273.6</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1171.1</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="5" t="n">
-        <v>46082</v>
-      </c>
-      <c r="C181" t="n">
-        <v>273.6</v>
-      </c>
-      <c r="D181" t="n">
-        <v>1175.4</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="n">
-        <v>46092</v>
-      </c>
-      <c r="C182" t="n">
-        <v>275.5</v>
-      </c>
-      <c r="D182" t="n">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="n">
-        <v>46102</v>
-      </c>
-      <c r="C183" t="n">
-        <v>275.4</v>
-      </c>
-      <c r="D183" t="n">
-        <v>1197.1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="n">
-        <v>46113</v>
-      </c>
-      <c r="C184" t="n">
-        <v>269.3</v>
-      </c>
-      <c r="D184" t="n">
-        <v>1191.4</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="5" t="n">
-        <v>46123</v>
-      </c>
-      <c r="C185" t="n">
-        <v>267</v>
-      </c>
-      <c r="D185" t="n">
-        <v>1176.1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="n">
-        <v>46133</v>
-      </c>
-      <c r="C186" t="n">
-        <v>263.6</v>
-      </c>
-      <c r="D186" t="n">
-        <v>1154.5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C187" t="n">
-        <v>259.6</v>
-      </c>
-      <c r="D187" t="n">
-        <v>1149.4</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="5" t="n">
-        <v>46153</v>
-      </c>
-      <c r="C188" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="D188" t="n">
-        <v>1150.3</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="5" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C189" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="D189" t="n">
-        <v>1140.1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="5" t="n">
-        <v>46174</v>
-      </c>
-      <c r="C190" t="n">
-        <v>260.5</v>
-      </c>
-      <c r="D190" t="n">
-        <v>1125.3</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="5" t="n">
-        <v>46184</v>
-      </c>
-      <c r="C191" t="n">
-        <v>260.2</v>
-      </c>
-      <c r="D191" t="n">
-        <v>1115.2</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="5" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C192" t="n">
-        <v>259.1</v>
-      </c>
-      <c r="D192" t="n">
-        <v>1113.5</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="5" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C193" t="n">
-        <v>256</v>
-      </c>
-      <c r="D193" t="n">
-        <v>1108.2</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="n">
-        <v>46214</v>
-      </c>
-      <c r="C194" t="n">
-        <v>250</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1100.4</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="5" t="n">
-        <v>46224</v>
-      </c>
-      <c r="C195" t="n">
-        <v>246.4</v>
-      </c>
-      <c r="D195" t="n">
-        <v>1098.9</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="5" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C196" t="n">
-        <v>246.8</v>
-      </c>
-      <c r="D196" t="n">
-        <v>1095.6</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="5" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C197" t="n">
-        <v>249.1</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1084.6</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="5" t="n">
-        <v>46255</v>
-      </c>
-      <c r="C198" t="n">
-        <v>248.7</v>
-      </c>
-      <c r="D198" t="n">
-        <v>1074.1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C199" t="n">
-        <v>250.7</v>
-      </c>
-      <c r="D199" t="n">
-        <v>1074.9</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="5" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C200" t="n">
-        <v>258.8</v>
-      </c>
-      <c r="D200" t="n">
-        <v>1101.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>